--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/KANSAS_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/KANSAS_2024.xlsx
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C174">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C263">
